--- a/requirement list 전태환.xlsx
+++ b/requirement list 전태환.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jth39\Documents\0 2026 1학기 문서\1 소프트웨어 공학\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33EE219-F5D7-4301-85D5-4315BC425012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE782DB-90E0-45B9-8976-EE574E853B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{97139AC8-D1E6-4E29-A305-152A3A9BE844}"/>
   </bookViews>
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>기능명</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>상세 설명 (Description)</t>
   </si>
@@ -111,9 +105,6 @@
   </si>
   <si>
     <t>회원은 검색된 리스트에서 설문을 선택하여 상세 정보를 조회할 수 있다.</t>
-  </si>
-  <si>
-    <t>내 응답 관리</t>
   </si>
   <si>
     <r>
@@ -178,12 +169,15 @@
   <si>
     <t>관리자는 특정 기간을 선택하여 전체 설문 수 및 응답 통계 수치를 조회할 수 있다.</t>
   </si>
+  <si>
+    <t>응답한 설문 조회 / 취소</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +205,14 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="6">
@@ -274,7 +276,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -303,6 +305,9 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -692,23 +697,17 @@
   <sheetFormatPr defaultColWidth="147.3984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.09765625" customWidth="1"/>
+    <col min="2" max="2" width="28.796875" customWidth="1"/>
     <col min="3" max="3" width="86.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -716,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -730,13 +729,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -744,13 +743,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -758,27 +757,27 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>24</v>
+      <c r="B6" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -786,13 +785,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -800,13 +799,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -814,13 +813,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>9</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -828,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -842,13 +841,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -856,13 +855,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.45">
@@ -870,13 +869,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
